--- a/data/atk_stat.xlsx
+++ b/data/atk_stat.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1312" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23F70314-48F2-40F9-B517-644DD900840D}"/>
+  <xr:revisionPtr revIDLastSave="1591" documentId="11_625D4987526768CFEB3B98154B5DCE3A47CD54D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{367E613E-3AD7-447C-BCAE-24529E5D0BD8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animus" sheetId="1" r:id="rId1"/>
     <sheet name="W017" sheetId="9" r:id="rId2"/>
+    <sheet name="W018" sheetId="10" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -856,7 +857,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="87">
   <si>
     <t>Animus</t>
   </si>
@@ -1241,6 +1242,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4001,4 +4006,1305 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8D7B9E-1A89-41B5-97AF-C25517CD6BD6}">
+  <dimension ref="A1:D91"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>40</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" t="s">
+        <v>72</v>
+      </c>
+      <c r="C58" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" t="s">
+        <v>57</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" t="s">
+        <v>57</v>
+      </c>
+      <c r="C62" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" t="s">
+        <v>78</v>
+      </c>
+      <c r="C64" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" t="s">
+        <v>37</v>
+      </c>
+      <c r="C67" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>61</v>
+      </c>
+      <c r="C69" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" t="s">
+        <v>40</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" t="s">
+        <v>76</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>57</v>
+      </c>
+      <c r="B73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" t="s">
+        <v>36</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>35</v>
+      </c>
+      <c r="C74" t="s">
+        <v>40</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" t="s">
+        <v>85</v>
+      </c>
+      <c r="C77" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>35</v>
+      </c>
+      <c r="B79" t="s">
+        <v>72</v>
+      </c>
+      <c r="C79" t="s">
+        <v>40</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" t="s">
+        <v>65</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>46</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>73</v>
+      </c>
+      <c r="B82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>71</v>
+      </c>
+      <c r="B83" t="s">
+        <v>40</v>
+      </c>
+      <c r="C83" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>73</v>
+      </c>
+      <c r="B84" t="s">
+        <v>33</v>
+      </c>
+      <c r="C84" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>70</v>
+      </c>
+      <c r="B86" t="s">
+        <v>73</v>
+      </c>
+      <c r="C86" t="s">
+        <v>36</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>37</v>
+      </c>
+      <c r="B87" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>65</v>
+      </c>
+      <c r="B88" t="s">
+        <v>48</v>
+      </c>
+      <c r="C88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" t="s">
+        <v>65</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" t="s">
+        <v>70</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>35</v>
+      </c>
+      <c r="B91" t="s">
+        <v>71</v>
+      </c>
+      <c r="C91" t="s">
+        <v>40</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8F897EBC-B8DA-4BC0-B921-3E52283D36DC}">
+          <x14:formula1>
+            <xm:f>Animus!$A$2:$A$82</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:C91</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
 </file>